--- a/Accounting_Journals_URL_List.xlsx
+++ b/Accounting_Journals_URL_List.xlsx
@@ -931,10 +931,14 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>0951-3574</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="n"/>
+          <t>1368-0668</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>1758-4205</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="13.5" customHeight="1">
       <c r="A9" s="1" t="n">
@@ -1617,7 +1621,7 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A*</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -1862,12 +1866,12 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>0020-7063</t>
+          <t>1094-4060</t>
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>1873-6548</t>
+          <t>2213-3933</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2802,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">De Gruyter </t>
+          <t>De Gruyter</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -2831,7 +2835,11 @@
           <t>2194-6051</t>
         </is>
       </c>
-      <c r="K43" s="1" t="n"/>
+      <c r="K43" s="1" t="inlineStr">
+        <is>
+          <t>2152-2820</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="13.5" customHeight="1">
       <c r="A44" s="1" t="n">
